--- a/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260908.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0052/ETF_Investment_Portfolio_20260908.xlsx
@@ -1305,17 +1305,17 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>6770</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>力積電</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>3,207,000</t>
+          <t>5,694,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>6770</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>力積電</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>5,694,000</t>
+          <t>3,207,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>2,585,703</t>
+          <t>7,136,249</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1547,17 +1547,17 @@
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>7,136,249</t>
+          <t>2,585,703</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>聯茂</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>388,000</t>
+          <t>93,000</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,17 +1657,17 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>202609WVHFU6F</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>富邦科技ETF期貨</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>388,000</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -1701,17 +1701,17 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>202609WVHFU6F</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>富世達</t>
+          <t>富邦科技ETF期貨</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>93,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1745,17 +1745,17 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>6531</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>愛普*</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>318,000</t>
+          <t>181,000</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -1767,17 +1767,17 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>801,000</t>
+          <t>772,000</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -1789,17 +1789,17 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>2492</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>華新科</t>
+          <t>禾伸堂</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>495,000</t>
+          <t>226,000</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -1811,17 +1811,17 @@
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>772,000</t>
+          <t>801,000</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -1833,17 +1833,17 @@
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>禾伸堂</t>
+          <t>華新科</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>226,000</t>
+          <t>495,000</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -1855,17 +1855,17 @@
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>愛普*</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>181,000</t>
+          <t>318,000</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -1877,17 +1877,17 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>宏碁</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>1,552,400</t>
+          <t>4,936,956</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -1899,17 +1899,17 @@
     <row r="80">
       <c r="A80" s="3" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>崇越</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>289,000</t>
+          <t>1,552,400</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -1921,17 +1921,17 @@
     <row r="81">
       <c r="A81" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>宏碁</t>
+          <t>崇越</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>4,936,956</t>
+          <t>289,000</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -1965,17 +1965,17 @@
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
         <is>
-          <t>2467</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>志聖</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>156,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -1987,17 +1987,17 @@
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>2451</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>創見</t>
+          <t>祥碩</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>330,000</t>
+          <t>65,538</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -2009,17 +2009,17 @@
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2467</t>
         </is>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>志聖</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>998,121</t>
+          <t>156,000</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>2451</t>
         </is>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>祥碩</t>
+          <t>創見</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>65,538</t>
+          <t>330,000</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -2053,17 +2053,17 @@
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>群光</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>998,121</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -2163,17 +2163,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>3532</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>台勝科</t>
+          <t>達發</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>114,000</t>
+          <t>71,000</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -2185,17 +2185,17 @@
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
         <is>
-          <t>6526</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>達發</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>71,000</t>
+          <t>114,000</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
